--- a/sampleData.xlsx
+++ b/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484163C0-9EB3-4ED8-9F45-DFA6A58DBD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5779CB-5239-47B8-9FFC-4D36264C58D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11431" uniqueCount="1458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11431" uniqueCount="1464">
   <si>
     <t>Contract Request ID</t>
   </si>
@@ -4413,6 +4413,24 @@
   </si>
   <si>
     <t>19/6/2025</t>
+  </si>
+  <si>
+    <t>2025-Agosto</t>
+  </si>
+  <si>
+    <t>2025-Octubre</t>
+  </si>
+  <si>
+    <t>2025-Julio</t>
+  </si>
+  <si>
+    <t>2025-Febrero</t>
+  </si>
+  <si>
+    <t>2025-Marzo</t>
+  </si>
+  <si>
+    <t>2025-April</t>
   </si>
 </sst>
 </file>
@@ -4925,6 +4943,8 @@
     <col min="14" max="14" width="22.36328125" customWidth="1"/>
     <col min="15" max="15" width="17.453125" customWidth="1"/>
     <col min="16" max="16" width="20.1796875" customWidth="1"/>
+    <col min="18" max="18" width="31.7265625" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
     <col min="22" max="22" width="26.08984375" customWidth="1"/>
     <col min="23" max="23" width="17.90625" customWidth="1"/>
     <col min="26" max="26" width="20.26953125" customWidth="1"/>
@@ -5537,7 +5557,7 @@
         <v>2025</v>
       </c>
       <c r="S3" s="15" t="s">
-        <v>1313</v>
+        <v>1462</v>
       </c>
       <c r="T3" s="15" t="s">
         <v>1314</v>
@@ -5797,8 +5817,8 @@
       <c r="R4" s="12">
         <v>2025</v>
       </c>
-      <c r="S4" s="12" t="s">
-        <v>1313</v>
+      <c r="S4" s="15" t="s">
+        <v>1462</v>
       </c>
       <c r="T4" s="12" t="s">
         <v>1314</v>
@@ -6059,7 +6079,7 @@
         <v>2025</v>
       </c>
       <c r="S5" s="15" t="s">
-        <v>1313</v>
+        <v>1462</v>
       </c>
       <c r="T5" s="15" t="s">
         <v>1314</v>
@@ -6315,8 +6335,8 @@
       <c r="R6" s="12">
         <v>2025</v>
       </c>
-      <c r="S6" s="12" t="s">
-        <v>1313</v>
+      <c r="S6" s="15" t="s">
+        <v>1462</v>
       </c>
       <c r="T6" s="12" t="s">
         <v>1314</v>
@@ -6831,8 +6851,8 @@
       <c r="R8" s="12">
         <v>2025</v>
       </c>
-      <c r="S8" s="12" t="s">
-        <v>1313</v>
+      <c r="S8" s="15" t="s">
+        <v>1462</v>
       </c>
       <c r="T8" s="12" t="s">
         <v>1314</v>
@@ -13562,7 +13582,7 @@
         <v>2025</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>1313</v>
+        <v>1458</v>
       </c>
       <c r="T34" s="12" t="s">
         <v>1314</v>
@@ -15618,7 +15638,7 @@
         <v>2025</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T42" s="12" t="s">
         <v>1314</v>
@@ -15878,8 +15898,8 @@
       <c r="R43" s="12">
         <v>2025</v>
       </c>
-      <c r="S43" s="15" t="s">
-        <v>1313</v>
+      <c r="S43" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T43" s="15" t="s">
         <v>1314</v>
@@ -16140,7 +16160,7 @@
         <v>2025</v>
       </c>
       <c r="S44" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T44" s="12" t="s">
         <v>1314</v>
@@ -16396,8 +16416,8 @@
       <c r="R45" s="12">
         <v>2025</v>
       </c>
-      <c r="S45" s="15" t="s">
-        <v>1313</v>
+      <c r="S45" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T45" s="15" t="s">
         <v>1314</v>
@@ -16658,7 +16678,7 @@
         <v>2025</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T46" s="12" t="s">
         <v>1314</v>
@@ -16916,8 +16936,8 @@
       <c r="R47" s="12">
         <v>2025</v>
       </c>
-      <c r="S47" s="15" t="s">
-        <v>1313</v>
+      <c r="S47" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T47" s="15" t="s">
         <v>1314</v>
@@ -17176,7 +17196,7 @@
         <v>2025</v>
       </c>
       <c r="S48" s="12" t="s">
-        <v>1313</v>
+        <v>1461</v>
       </c>
       <c r="T48" s="12" t="s">
         <v>1314</v>
@@ -17436,8 +17456,8 @@
       <c r="R49" s="12">
         <v>2025</v>
       </c>
-      <c r="S49" s="15" t="s">
-        <v>1313</v>
+      <c r="S49" s="12" t="s">
+        <v>1461</v>
       </c>
       <c r="T49" s="15" t="s">
         <v>1314</v>
@@ -17696,7 +17716,7 @@
         <v>2025</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T50" s="12" t="s">
         <v>1288</v>
@@ -17954,8 +17974,8 @@
       <c r="R51" s="12">
         <v>2025</v>
       </c>
-      <c r="S51" s="15" t="s">
-        <v>1313</v>
+      <c r="S51" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T51" s="15" t="s">
         <v>1314</v>
@@ -18212,7 +18232,7 @@
         <v>2025</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T52" s="12" t="s">
         <v>1314</v>
@@ -18468,8 +18488,8 @@
       <c r="R53" s="12">
         <v>2025</v>
       </c>
-      <c r="S53" s="15" t="s">
-        <v>1313</v>
+      <c r="S53" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T53" s="15" t="s">
         <v>1314</v>
@@ -18730,7 +18750,7 @@
         <v>2025</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T54" s="12" t="s">
         <v>1314</v>
@@ -18990,8 +19010,8 @@
       <c r="R55" s="12">
         <v>2025</v>
       </c>
-      <c r="S55" s="15" t="s">
-        <v>1313</v>
+      <c r="S55" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T55" s="15" t="s">
         <v>1314</v>
@@ -19246,7 +19266,7 @@
         <v>2025</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T56" s="12" t="s">
         <v>1314</v>
@@ -19500,8 +19520,8 @@
       <c r="R57" s="12">
         <v>2025</v>
       </c>
-      <c r="S57" s="15" t="s">
-        <v>1313</v>
+      <c r="S57" s="12" t="s">
+        <v>1459</v>
       </c>
       <c r="T57" s="15" t="s">
         <v>1314</v>
@@ -19762,7 +19782,7 @@
         <v>2025</v>
       </c>
       <c r="S58" s="12" t="s">
-        <v>1313</v>
+        <v>1459</v>
       </c>
       <c r="T58" s="12" t="s">
         <v>1314</v>
@@ -22856,7 +22876,7 @@
         <v>2025</v>
       </c>
       <c r="S70" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T70" s="12" t="s">
         <v>1314</v>
@@ -23112,8 +23132,8 @@
       <c r="R71" s="12">
         <v>2025</v>
       </c>
-      <c r="S71" s="15" t="s">
-        <v>1313</v>
+      <c r="S71" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T71" s="15" t="s">
         <v>1314</v>
@@ -23374,7 +23394,7 @@
         <v>2025</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T72" s="12" t="s">
         <v>1314</v>
@@ -23634,8 +23654,8 @@
       <c r="R73" s="12">
         <v>2025</v>
       </c>
-      <c r="S73" s="15" t="s">
-        <v>1313</v>
+      <c r="S73" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T73" s="15" t="s">
         <v>1288</v>
@@ -23896,7 +23916,7 @@
         <v>2025</v>
       </c>
       <c r="S74" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T74" s="12" t="s">
         <v>1314</v>
@@ -24156,8 +24176,8 @@
       <c r="R75" s="12">
         <v>2025</v>
       </c>
-      <c r="S75" s="15" t="s">
-        <v>1313</v>
+      <c r="S75" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T75" s="15" t="s">
         <v>1314</v>
@@ -24418,7 +24438,7 @@
         <v>2025</v>
       </c>
       <c r="S76" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T76" s="12" t="s">
         <v>1288</v>
@@ -24678,8 +24698,8 @@
       <c r="R77" s="12">
         <v>2025</v>
       </c>
-      <c r="S77" s="15" t="s">
-        <v>1313</v>
+      <c r="S77" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T77" s="15" t="s">
         <v>1288</v>
@@ -24940,7 +24960,7 @@
         <v>2025</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T78" s="12" t="s">
         <v>1288</v>
@@ -25200,8 +25220,8 @@
       <c r="R79" s="12">
         <v>2025</v>
       </c>
-      <c r="S79" s="15" t="s">
-        <v>1313</v>
+      <c r="S79" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T79" s="15" t="s">
         <v>1288</v>
@@ -25462,7 +25482,7 @@
         <v>2025</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T80" s="12" t="s">
         <v>1288</v>
@@ -25722,8 +25742,8 @@
       <c r="R81" s="12">
         <v>2025</v>
       </c>
-      <c r="S81" s="15" t="s">
-        <v>1313</v>
+      <c r="S81" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T81" s="15" t="s">
         <v>1288</v>
@@ -25976,7 +25996,7 @@
         <v>2025</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T82" s="12" t="s">
         <v>1288</v>
@@ -26234,8 +26254,8 @@
       <c r="R83" s="12">
         <v>2025</v>
       </c>
-      <c r="S83" s="15" t="s">
-        <v>1313</v>
+      <c r="S83" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T83" s="15" t="s">
         <v>1288</v>
@@ -26488,7 +26508,7 @@
         <v>2025</v>
       </c>
       <c r="S84" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T84" s="12" t="s">
         <v>1288</v>
@@ -26742,8 +26762,8 @@
       <c r="R85" s="12">
         <v>2025</v>
       </c>
-      <c r="S85" s="15" t="s">
-        <v>1313</v>
+      <c r="S85" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T85" s="15" t="s">
         <v>1314</v>
@@ -27002,7 +27022,7 @@
         <v>2025</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T86" s="12" t="s">
         <v>1288</v>
@@ -27262,8 +27282,8 @@
       <c r="R87" s="12">
         <v>2025</v>
       </c>
-      <c r="S87" s="15" t="s">
-        <v>1313</v>
+      <c r="S87" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T87" s="15" t="s">
         <v>1314</v>
@@ -27520,7 +27540,7 @@
         <v>2025</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T88" s="12" t="s">
         <v>1288</v>
@@ -27780,8 +27800,8 @@
       <c r="R89" s="12">
         <v>2025</v>
       </c>
-      <c r="S89" s="15" t="s">
-        <v>1313</v>
+      <c r="S89" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T89" s="15" t="s">
         <v>1288</v>
@@ -28040,7 +28060,7 @@
         <v>2025</v>
       </c>
       <c r="S90" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T90" s="12" t="s">
         <v>1288</v>
@@ -28298,8 +28318,8 @@
       <c r="R91" s="12">
         <v>2025</v>
       </c>
-      <c r="S91" s="15" t="s">
-        <v>1313</v>
+      <c r="S91" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T91" s="15" t="s">
         <v>1314</v>
@@ -28560,7 +28580,7 @@
         <v>2025</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T92" s="12" t="s">
         <v>1288</v>
@@ -28818,8 +28838,8 @@
       <c r="R93" s="12">
         <v>2025</v>
       </c>
-      <c r="S93" s="15" t="s">
-        <v>1313</v>
+      <c r="S93" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T93" s="15" t="s">
         <v>1288</v>
@@ -29080,7 +29100,7 @@
         <v>2025</v>
       </c>
       <c r="S94" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T94" s="12" t="s">
         <v>1288</v>
@@ -29340,8 +29360,8 @@
       <c r="R95" s="12">
         <v>2025</v>
       </c>
-      <c r="S95" s="15" t="s">
-        <v>1313</v>
+      <c r="S95" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T95" s="15" t="s">
         <v>1314</v>
@@ -29602,7 +29622,7 @@
         <v>2025</v>
       </c>
       <c r="S96" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T96" s="12" t="s">
         <v>1314</v>
@@ -29862,8 +29882,8 @@
       <c r="R97" s="12">
         <v>2025</v>
       </c>
-      <c r="S97" s="15" t="s">
-        <v>1313</v>
+      <c r="S97" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T97" s="15" t="s">
         <v>1314</v>
@@ -30116,7 +30136,7 @@
         <v>2025</v>
       </c>
       <c r="S98" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T98" s="12" t="s">
         <v>1288</v>
@@ -30368,8 +30388,8 @@
       <c r="R99" s="12">
         <v>2025</v>
       </c>
-      <c r="S99" s="15" t="s">
-        <v>1313</v>
+      <c r="S99" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T99" s="15" t="s">
         <v>1314</v>
@@ -30630,7 +30650,7 @@
         <v>2025</v>
       </c>
       <c r="S100" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T100" s="12" t="s">
         <v>1314</v>
@@ -30888,8 +30908,8 @@
       <c r="R101" s="12">
         <v>2025</v>
       </c>
-      <c r="S101" s="15" t="s">
-        <v>1313</v>
+      <c r="S101" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T101" s="15" t="s">
         <v>1314</v>
@@ -31150,7 +31170,7 @@
         <v>2025</v>
       </c>
       <c r="S102" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T102" s="12" t="s">
         <v>1288</v>
@@ -31410,8 +31430,8 @@
       <c r="R103" s="12">
         <v>2025</v>
       </c>
-      <c r="S103" s="15" t="s">
-        <v>1313</v>
+      <c r="S103" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T103" s="15" t="s">
         <v>1288</v>
@@ -31666,7 +31686,7 @@
         <v>2025</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T104" s="12" t="s">
         <v>1288</v>
@@ -31924,8 +31944,8 @@
       <c r="R105" s="12">
         <v>2025</v>
       </c>
-      <c r="S105" s="15" t="s">
-        <v>1313</v>
+      <c r="S105" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T105" s="15" t="s">
         <v>1288</v>
@@ -32180,7 +32200,7 @@
         <v>2025</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T106" s="12" t="s">
         <v>1288</v>
@@ -32440,8 +32460,8 @@
       <c r="R107" s="12">
         <v>2025</v>
       </c>
-      <c r="S107" s="15" t="s">
-        <v>1313</v>
+      <c r="S107" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T107" s="15" t="s">
         <v>1288</v>
@@ -32696,7 +32716,7 @@
         <v>2025</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>1313</v>
+        <v>1463</v>
       </c>
       <c r="T108" s="12" t="s">
         <v>1288</v>
@@ -32950,8 +32970,8 @@
       <c r="R109" s="12">
         <v>2025</v>
       </c>
-      <c r="S109" s="15" t="s">
-        <v>1313</v>
+      <c r="S109" s="12" t="s">
+        <v>1463</v>
       </c>
       <c r="T109" s="15" t="s">
         <v>1288</v>
@@ -62566,7 +62586,7 @@
         <v>2025</v>
       </c>
       <c r="S257" s="15" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T257" s="15" t="s">
         <v>1314</v>
@@ -62762,7 +62782,7 @@
         <v>2025</v>
       </c>
       <c r="S258" s="12" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T258" s="12" t="s">
         <v>1314</v>
@@ -62952,7 +62972,7 @@
         <v>2025</v>
       </c>
       <c r="S259" s="15" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T259" s="15" t="s">
         <v>1314</v>
@@ -63150,7 +63170,7 @@
         <v>2025</v>
       </c>
       <c r="S260" s="12" t="s">
-        <v>1313</v>
+        <v>1460</v>
       </c>
       <c r="T260" s="12" t="s">
         <v>1314</v>
@@ -64644,7 +64664,7 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 O2:CK111 O112:BN285" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
+    <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A1:N2 A260:N260 O1:CH1 O112:BN285 O2:CK111" name="All Access Jorge H" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A3:N5" name="All Access Jorge H_1" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A6:N6" name="All Access Jorge H_2" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A7:N9" name="All Access Jorge H_3" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>

--- a/sampleData.xlsx
+++ b/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5779CB-5239-47B8-9FFC-4D36264C58D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{381E9962-C8DA-4D74-9E65-34D3D81CFB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -4944,7 +4944,7 @@
     <col min="15" max="15" width="17.453125" customWidth="1"/>
     <col min="16" max="16" width="20.1796875" customWidth="1"/>
     <col min="18" max="18" width="31.7265625" customWidth="1"/>
-    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="19" max="19" width="36.6328125" customWidth="1"/>
     <col min="22" max="22" width="26.08984375" customWidth="1"/>
     <col min="23" max="23" width="17.90625" customWidth="1"/>
     <col min="26" max="26" width="20.26953125" customWidth="1"/>

--- a/sampleData.xlsx
+++ b/sampleData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U45555\IT-dashboard\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D82B5FF-91C6-4D90-9C89-9A24B08035B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5D08D8-F38A-4775-84A6-2C0BB3066CF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{724309DC-2642-42C3-9093-42F88D91BE1B}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$CK$306</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$CK$326</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5842,7 +5842,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:CK326"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6165,7 +6164,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="2" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -6426,7 +6425,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="3" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -6687,7 +6686,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="4" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
@@ -6948,7 +6947,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="5" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>44</v>
       </c>
@@ -7205,7 +7204,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="6" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>48</v>
       </c>
@@ -7466,7 +7465,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="7" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>55</v>
       </c>
@@ -7721,7 +7720,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="8" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>60</v>
       </c>
@@ -7980,7 +7979,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="9" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>64</v>
       </c>
@@ -8241,7 +8240,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="10" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>72</v>
       </c>
@@ -8500,7 +8499,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="11" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>79</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="12" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>84</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="13" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>89</v>
       </c>
@@ -9275,7 +9274,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="14" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
         <v>93</v>
       </c>
@@ -9536,7 +9535,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="15" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>98</v>
       </c>
@@ -10052,7 +10051,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="17" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>107</v>
       </c>
@@ -10313,7 +10312,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="18" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>116</v>
       </c>
@@ -10570,7 +10569,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="19" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>120</v>
       </c>
@@ -10831,7 +10830,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="20" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
         <v>127</v>
       </c>
@@ -11092,7 +11091,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="21" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>134</v>
       </c>
@@ -11353,7 +11352,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="22" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
         <v>143</v>
       </c>
@@ -11610,7 +11609,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="23" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>148</v>
       </c>
@@ -11869,7 +11868,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="24" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>155</v>
       </c>
@@ -12130,7 +12129,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="25" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>161</v>
       </c>
@@ -12383,7 +12382,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="26" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>166</v>
       </c>
@@ -12644,7 +12643,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="27" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>170</v>
       </c>
@@ -12905,7 +12904,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="28" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>174</v>
       </c>
@@ -13162,7 +13161,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="29" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>178</v>
       </c>
@@ -13423,7 +13422,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="30" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>183</v>
       </c>
@@ -13682,7 +13681,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="31" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>187</v>
       </c>
@@ -13939,7 +13938,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="32" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
@@ -14190,7 +14189,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="33" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>199</v>
       </c>
@@ -14451,7 +14450,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="34" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>205</v>
       </c>
@@ -14708,7 +14707,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="35" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>209</v>
       </c>
@@ -14965,7 +14964,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="36" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>213</v>
       </c>
@@ -15220,7 +15219,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="37" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>217</v>
       </c>
@@ -15481,7 +15480,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="38" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>221</v>
       </c>
@@ -15742,7 +15741,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="39" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>225</v>
       </c>
@@ -16003,7 +16002,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="40" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>229</v>
       </c>
@@ -16256,7 +16255,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="41" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>233</v>
       </c>
@@ -16507,7 +16506,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="42" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>237</v>
       </c>
@@ -16768,7 +16767,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="43" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>241</v>
       </c>
@@ -17029,7 +17028,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="44" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
         <v>245</v>
       </c>
@@ -17286,7 +17285,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="45" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>249</v>
       </c>
@@ -17547,7 +17546,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="46" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
         <v>253</v>
       </c>
@@ -17806,7 +17805,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="47" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>257</v>
       </c>
@@ -18065,7 +18064,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="48" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
         <v>262</v>
       </c>
@@ -18326,7 +18325,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="49" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>266</v>
       </c>
@@ -18585,7 +18584,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="50" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
         <v>270</v>
       </c>
@@ -18844,7 +18843,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="51" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>276</v>
       </c>
@@ -19101,7 +19100,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="52" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
         <v>280</v>
       </c>
@@ -19358,7 +19357,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="53" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>284</v>
       </c>
@@ -19619,7 +19618,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="54" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
         <v>289</v>
       </c>
@@ -19880,7 +19879,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="55" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>294</v>
       </c>
@@ -20135,7 +20134,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="56" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>298</v>
       </c>
@@ -20390,7 +20389,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="57" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>302</v>
       </c>
@@ -20651,7 +20650,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="58" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>306</v>
       </c>
@@ -20912,7 +20911,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="59" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>310</v>
       </c>
@@ -21173,7 +21172,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="60" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>314</v>
       </c>
@@ -21430,7 +21429,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="61" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>318</v>
       </c>
@@ -21691,7 +21690,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="62" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>323</v>
       </c>
@@ -21948,7 +21947,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="63" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>329</v>
       </c>
@@ -22205,7 +22204,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="64" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A64" s="7" t="s">
         <v>333</v>
       </c>
@@ -22462,7 +22461,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="65" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>337</v>
       </c>
@@ -22723,7 +22722,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="66" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A66" s="7" t="s">
         <v>341</v>
       </c>
@@ -22984,7 +22983,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="67" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>345</v>
       </c>
@@ -23237,7 +23236,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="68" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A68" s="7" t="s">
         <v>349</v>
       </c>
@@ -23492,7 +23491,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="69" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>356</v>
       </c>
@@ -23745,7 +23744,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="70" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A70" s="7" t="s">
         <v>360</v>
       </c>
@@ -24002,7 +24001,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="71" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>364</v>
       </c>
@@ -24263,7 +24262,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="72" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A72" s="7" t="s">
         <v>369</v>
       </c>
@@ -24524,7 +24523,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="73" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>373</v>
       </c>
@@ -24785,7 +24784,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="74" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>377</v>
       </c>
@@ -25046,7 +25045,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="75" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>381</v>
       </c>
@@ -25307,7 +25306,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="76" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>385</v>
       </c>
@@ -25568,7 +25567,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="77" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>389</v>
       </c>
@@ -25829,7 +25828,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="78" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A78" s="7" t="s">
         <v>393</v>
       </c>
@@ -26090,7 +26089,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="79" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>397</v>
       </c>
@@ -26351,7 +26350,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="80" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A80" s="7" t="s">
         <v>401</v>
       </c>
@@ -26612,7 +26611,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="81" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>405</v>
       </c>
@@ -27124,7 +27123,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="83" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>413</v>
       </c>
@@ -27379,7 +27378,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="84" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>419</v>
       </c>
@@ -27632,7 +27631,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="85" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>425</v>
       </c>
@@ -27893,7 +27892,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="86" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>430</v>
       </c>
@@ -28152,7 +28151,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="87" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>433</v>
       </c>
@@ -28409,7 +28408,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="88" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>440</v>
       </c>
@@ -28670,7 +28669,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="89" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>444</v>
       </c>
@@ -28929,7 +28928,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="90" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
         <v>449</v>
       </c>
@@ -29188,7 +29187,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="91" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>454</v>
       </c>
@@ -29449,7 +29448,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="92" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
         <v>458</v>
       </c>
@@ -29708,7 +29707,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="93" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>462</v>
       </c>
@@ -29969,7 +29968,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="94" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
         <v>470</v>
       </c>
@@ -30230,7 +30229,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="95" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>475</v>
       </c>
@@ -30491,7 +30490,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="96" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
         <v>480</v>
       </c>
@@ -30752,7 +30751,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="97" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>484</v>
       </c>
@@ -31005,7 +31004,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="98" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>488</v>
       </c>
@@ -31258,7 +31257,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="99" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>493</v>
       </c>
@@ -31519,7 +31518,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="100" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
         <v>499</v>
       </c>
@@ -31778,7 +31777,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="101" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>503</v>
       </c>
@@ -32039,7 +32038,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="102" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
         <v>507</v>
       </c>
@@ -32300,7 +32299,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="103" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>511</v>
       </c>
@@ -32555,7 +32554,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="104" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>515</v>
       </c>
@@ -32816,7 +32815,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="105" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>520</v>
       </c>
@@ -33069,7 +33068,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="106" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
         <v>523</v>
       </c>
@@ -33330,7 +33329,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="107" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>527</v>
       </c>
@@ -33585,7 +33584,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="108" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
         <v>531</v>
       </c>
@@ -33840,7 +33839,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="109" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>535</v>
       </c>
@@ -34101,7 +34100,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="110" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>539</v>
       </c>
@@ -34360,7 +34359,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="111" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>543</v>
       </c>
@@ -34621,7 +34620,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="112" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
         <v>547</v>
       </c>
@@ -34870,7 +34869,7 @@
         <v>787130.2</v>
       </c>
     </row>
-    <row r="113" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>551</v>
       </c>
@@ -35119,7 +35118,7 @@
         <v>787131.2</v>
       </c>
     </row>
-    <row r="114" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
         <v>555</v>
       </c>
@@ -35368,7 +35367,7 @@
         <v>787132.2</v>
       </c>
     </row>
-    <row r="115" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>559</v>
       </c>
@@ -35615,7 +35614,7 @@
         <v>787133.2</v>
       </c>
     </row>
-    <row r="116" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
         <v>563</v>
       </c>
@@ -35864,7 +35863,7 @@
         <v>787134.2</v>
       </c>
     </row>
-    <row r="117" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>567</v>
       </c>
@@ -36109,7 +36108,7 @@
         <v>787135.2</v>
       </c>
     </row>
-    <row r="118" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
         <v>571</v>
       </c>
@@ -36358,7 +36357,7 @@
         <v>787136.2</v>
       </c>
     </row>
-    <row r="119" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>575</v>
       </c>
@@ -36607,7 +36606,7 @@
         <v>787137.2</v>
       </c>
     </row>
-    <row r="120" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
         <v>579</v>
       </c>
@@ -36856,7 +36855,7 @@
         <v>787138.2</v>
       </c>
     </row>
-    <row r="121" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>583</v>
       </c>
@@ -37105,7 +37104,7 @@
         <v>787139.2</v>
       </c>
     </row>
-    <row r="122" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
         <v>589</v>
       </c>
@@ -37354,7 +37353,7 @@
         <v>787140.2</v>
       </c>
     </row>
-    <row r="123" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>595</v>
       </c>
@@ -37599,7 +37598,7 @@
         <v>787141.2</v>
       </c>
     </row>
-    <row r="124" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>600</v>
       </c>
@@ -37846,7 +37845,7 @@
         <v>787142.2</v>
       </c>
     </row>
-    <row r="125" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>604</v>
       </c>
@@ -38089,7 +38088,7 @@
         <v>787143.2</v>
       </c>
     </row>
-    <row r="126" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>607</v>
       </c>
@@ -38336,7 +38335,7 @@
         <v>787144.2</v>
       </c>
     </row>
-    <row r="127" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>610</v>
       </c>
@@ -38585,7 +38584,7 @@
         <v>787145.2</v>
       </c>
     </row>
-    <row r="128" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>615</v>
       </c>
@@ -38830,7 +38829,7 @@
         <v>787146.2</v>
       </c>
     </row>
-    <row r="129" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>618</v>
       </c>
@@ -39091,7 +39090,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="130" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A130" s="7" t="s">
         <v>622</v>
       </c>
@@ -39340,7 +39339,7 @@
         <v>787148.2</v>
       </c>
     </row>
-    <row r="131" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>627</v>
       </c>
@@ -39589,7 +39588,7 @@
         <v>787149.2</v>
       </c>
     </row>
-    <row r="132" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A132" s="7" t="s">
         <v>631</v>
       </c>
@@ -39836,7 +39835,7 @@
         <v>787150.2</v>
       </c>
     </row>
-    <row r="133" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>635</v>
       </c>
@@ -40097,7 +40096,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="134" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>641</v>
       </c>
@@ -40346,7 +40345,7 @@
         <v>787152.2</v>
       </c>
     </row>
-    <row r="135" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>645</v>
       </c>
@@ -40589,7 +40588,7 @@
         <v>787153.2</v>
       </c>
     </row>
-    <row r="136" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A136" s="7" t="s">
         <v>650</v>
       </c>
@@ -40838,7 +40837,7 @@
         <v>787154.2</v>
       </c>
     </row>
-    <row r="137" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>655</v>
       </c>
@@ -41087,7 +41086,7 @@
         <v>787155.2</v>
       </c>
     </row>
-    <row r="138" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A138" s="7" t="s">
         <v>660</v>
       </c>
@@ -41334,7 +41333,7 @@
         <v>787156.2</v>
       </c>
     </row>
-    <row r="139" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>664</v>
       </c>
@@ -41583,7 +41582,7 @@
         <v>787157.2</v>
       </c>
     </row>
-    <row r="140" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A140" s="7" t="s">
         <v>669</v>
       </c>
@@ -41832,7 +41831,7 @@
         <v>787158.2</v>
       </c>
     </row>
-    <row r="141" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>673</v>
       </c>
@@ -42079,7 +42078,7 @@
         <v>787159.2</v>
       </c>
     </row>
-    <row r="142" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>677</v>
       </c>
@@ -42320,7 +42319,7 @@
         <v>787160.2</v>
       </c>
     </row>
-    <row r="143" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>682</v>
       </c>
@@ -42567,7 +42566,7 @@
         <v>787161.2</v>
       </c>
     </row>
-    <row r="144" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>687</v>
       </c>
@@ -42814,7 +42813,7 @@
         <v>787162.2</v>
       </c>
     </row>
-    <row r="145" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>691</v>
       </c>
@@ -43061,7 +43060,7 @@
         <v>787163.2</v>
       </c>
     </row>
-    <row r="146" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>695</v>
       </c>
@@ -43310,7 +43309,7 @@
         <v>787164.2</v>
       </c>
     </row>
-    <row r="147" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>700</v>
       </c>
@@ -43559,7 +43558,7 @@
         <v>787165.2</v>
       </c>
     </row>
-    <row r="148" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>704</v>
       </c>
@@ -43808,7 +43807,7 @@
         <v>787166.2</v>
       </c>
     </row>
-    <row r="149" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>708</v>
       </c>
@@ -44057,7 +44056,7 @@
         <v>787167.2</v>
       </c>
     </row>
-    <row r="150" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A150" s="7" t="s">
         <v>713</v>
       </c>
@@ -44304,7 +44303,7 @@
         <v>787168.2</v>
       </c>
     </row>
-    <row r="151" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>718</v>
       </c>
@@ -44551,7 +44550,7 @@
         <v>787169.2</v>
       </c>
     </row>
-    <row r="152" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A152" s="7" t="s">
         <v>722</v>
       </c>
@@ -44800,7 +44799,7 @@
         <v>787170.2</v>
       </c>
     </row>
-    <row r="153" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>726</v>
       </c>
@@ -45049,7 +45048,7 @@
         <v>787171.2</v>
       </c>
     </row>
-    <row r="154" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A154" s="7" t="s">
         <v>732</v>
       </c>
@@ -45294,7 +45293,7 @@
         <v>787172.2</v>
       </c>
     </row>
-    <row r="155" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>736</v>
       </c>
@@ -45541,7 +45540,7 @@
         <v>787173.2</v>
       </c>
     </row>
-    <row r="156" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A156" s="7" t="s">
         <v>739</v>
       </c>
@@ -45788,7 +45787,7 @@
         <v>787174.2</v>
       </c>
     </row>
-    <row r="157" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>742</v>
       </c>
@@ -46037,7 +46036,7 @@
         <v>787175.2</v>
       </c>
     </row>
-    <row r="158" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A158" s="7" t="s">
         <v>746</v>
       </c>
@@ -46284,7 +46283,7 @@
         <v>787176.2</v>
       </c>
     </row>
-    <row r="159" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>749</v>
       </c>
@@ -46533,7 +46532,7 @@
         <v>787177.2</v>
       </c>
     </row>
-    <row r="160" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A160" s="7" t="s">
         <v>753</v>
       </c>
@@ -46780,7 +46779,7 @@
         <v>787178.2</v>
       </c>
     </row>
-    <row r="161" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>756</v>
       </c>
@@ -47027,7 +47026,7 @@
         <v>787179.2</v>
       </c>
     </row>
-    <row r="162" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A162" s="7" t="s">
         <v>761</v>
       </c>
@@ -47274,7 +47273,7 @@
         <v>787180.2</v>
       </c>
     </row>
-    <row r="163" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>766</v>
       </c>
@@ -47535,7 +47534,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="164" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A164" s="7" t="s">
         <v>771</v>
       </c>
@@ -47784,7 +47783,7 @@
         <v>787182.2</v>
       </c>
     </row>
-    <row r="165" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>775</v>
       </c>
@@ -48029,7 +48028,7 @@
         <v>787183.2</v>
       </c>
     </row>
-    <row r="166" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A166" s="7" t="s">
         <v>779</v>
       </c>
@@ -48274,7 +48273,7 @@
         <v>787184.2</v>
       </c>
     </row>
-    <row r="167" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>783</v>
       </c>
@@ -48535,7 +48534,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="168" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>788</v>
       </c>
@@ -48784,7 +48783,7 @@
         <v>787186.2</v>
       </c>
     </row>
-    <row r="169" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>793</v>
       </c>
@@ -49045,7 +49044,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="170" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A170" s="7" t="s">
         <v>797</v>
       </c>
@@ -49294,7 +49293,7 @@
         <v>787188.2</v>
       </c>
     </row>
-    <row r="171" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>801</v>
       </c>
@@ -49555,7 +49554,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="172" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>806</v>
       </c>
@@ -49804,7 +49803,7 @@
         <v>787190.2</v>
       </c>
     </row>
-    <row r="173" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>811</v>
       </c>
@@ -50051,7 +50050,7 @@
         <v>787191.2</v>
       </c>
     </row>
-    <row r="174" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>815</v>
       </c>
@@ -50300,7 +50299,7 @@
         <v>787192.2</v>
       </c>
     </row>
-    <row r="175" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>819</v>
       </c>
@@ -50545,7 +50544,7 @@
         <v>787193.2</v>
       </c>
     </row>
-    <row r="176" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A176" s="7" t="s">
         <v>823</v>
       </c>
@@ -50806,7 +50805,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="177" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>828</v>
       </c>
@@ -51055,7 +51054,7 @@
         <v>787195.2</v>
       </c>
     </row>
-    <row r="178" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>833</v>
       </c>
@@ -51316,7 +51315,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="179" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>837</v>
       </c>
@@ -51577,7 +51576,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="180" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>841</v>
       </c>
@@ -51826,7 +51825,7 @@
         <v>787198.2</v>
       </c>
     </row>
-    <row r="181" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>846</v>
       </c>
@@ -52071,7 +52070,7 @@
         <v>787199.2</v>
       </c>
     </row>
-    <row r="182" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>850</v>
       </c>
@@ -52320,7 +52319,7 @@
         <v>787200.2</v>
       </c>
     </row>
-    <row r="183" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>854</v>
       </c>
@@ -52565,7 +52564,7 @@
         <v>787201.2</v>
       </c>
     </row>
-    <row r="184" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>859</v>
       </c>
@@ -52814,7 +52813,7 @@
         <v>787202.2</v>
       </c>
     </row>
-    <row r="185" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>863</v>
       </c>
@@ -53063,7 +53062,7 @@
         <v>787203.2</v>
       </c>
     </row>
-    <row r="186" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>869</v>
       </c>
@@ -53310,7 +53309,7 @@
         <v>787204.2</v>
       </c>
     </row>
-    <row r="187" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>874</v>
       </c>
@@ -53559,7 +53558,7 @@
         <v>787205.2</v>
       </c>
     </row>
-    <row r="188" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A188" s="7" t="s">
         <v>878</v>
       </c>
@@ -53808,7 +53807,7 @@
         <v>787206.2</v>
       </c>
     </row>
-    <row r="189" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>882</v>
       </c>
@@ -54057,7 +54056,7 @@
         <v>787207.2</v>
       </c>
     </row>
-    <row r="190" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A190" s="7" t="s">
         <v>886</v>
       </c>
@@ -54304,7 +54303,7 @@
         <v>787208.2</v>
       </c>
     </row>
-    <row r="191" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>890</v>
       </c>
@@ -54553,7 +54552,7 @@
         <v>787209.2</v>
       </c>
     </row>
-    <row r="192" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>894</v>
       </c>
@@ -54814,7 +54813,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="193" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
         <v>898</v>
       </c>
@@ -55057,7 +55056,7 @@
         <v>787211.2</v>
       </c>
     </row>
-    <row r="194" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>903</v>
       </c>
@@ -55306,7 +55305,7 @@
         <v>787212.2</v>
       </c>
     </row>
-    <row r="195" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>907</v>
       </c>
@@ -55555,7 +55554,7 @@
         <v>787213.2</v>
       </c>
     </row>
-    <row r="196" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>911</v>
       </c>
@@ -55802,7 +55801,7 @@
         <v>787214.2</v>
       </c>
     </row>
-    <row r="197" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
         <v>915</v>
       </c>
@@ -56051,7 +56050,7 @@
         <v>787215.2</v>
       </c>
     </row>
-    <row r="198" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>920</v>
       </c>
@@ -56300,7 +56299,7 @@
         <v>787216.2</v>
       </c>
     </row>
-    <row r="199" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>925</v>
       </c>
@@ -56547,7 +56546,7 @@
         <v>787217.2</v>
       </c>
     </row>
-    <row r="200" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>930</v>
       </c>
@@ -56788,7 +56787,7 @@
         <v>787218.2</v>
       </c>
     </row>
-    <row r="201" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>936</v>
       </c>
@@ -57037,7 +57036,7 @@
         <v>787219.2</v>
       </c>
     </row>
-    <row r="202" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>940</v>
       </c>
@@ -57284,7 +57283,7 @@
         <v>787220.2</v>
       </c>
     </row>
-    <row r="203" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A203" s="7" t="s">
         <v>944</v>
       </c>
@@ -57531,7 +57530,7 @@
         <v>787221.2</v>
       </c>
     </row>
-    <row r="204" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>948</v>
       </c>
@@ -57780,7 +57779,7 @@
         <v>787222.2</v>
       </c>
     </row>
-    <row r="205" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
         <v>952</v>
       </c>
@@ -58029,7 +58028,7 @@
         <v>787223.2</v>
       </c>
     </row>
-    <row r="206" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A206" s="7" t="s">
         <v>957</v>
       </c>
@@ -58278,7 +58277,7 @@
         <v>787224.2</v>
       </c>
     </row>
-    <row r="207" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
         <v>963</v>
       </c>
@@ -58527,7 +58526,7 @@
         <v>787225.2</v>
       </c>
     </row>
-    <row r="208" spans="1:85" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:85" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>967</v>
       </c>
@@ -58776,7 +58775,7 @@
         <v>787226.2</v>
       </c>
     </row>
-    <row r="209" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>971</v>
       </c>
@@ -59023,7 +59022,7 @@
         <v>787227.2</v>
       </c>
     </row>
-    <row r="210" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>977</v>
       </c>
@@ -59519,7 +59518,7 @@
         <v>787229.2</v>
       </c>
     </row>
-    <row r="212" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A212" s="7" t="s">
         <v>986</v>
       </c>
@@ -59778,7 +59777,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="213" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>991</v>
       </c>
@@ -60027,7 +60026,7 @@
         <v>787231.2</v>
       </c>
     </row>
-    <row r="214" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A214" s="7" t="s">
         <v>999</v>
       </c>
@@ -60276,7 +60275,7 @@
         <v>787232.2</v>
       </c>
     </row>
-    <row r="215" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
         <v>1005</v>
       </c>
@@ -60525,7 +60524,7 @@
         <v>787233.2</v>
       </c>
     </row>
-    <row r="216" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A216" s="7" t="s">
         <v>1009</v>
       </c>
@@ -60774,7 +60773,7 @@
         <v>787234.2</v>
       </c>
     </row>
-    <row r="217" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
         <v>1013</v>
       </c>
@@ -61023,7 +61022,7 @@
         <v>787235.2</v>
       </c>
     </row>
-    <row r="218" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A218" s="7" t="s">
         <v>1017</v>
       </c>
@@ -61272,7 +61271,7 @@
         <v>787236.2</v>
       </c>
     </row>
-    <row r="219" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>1021</v>
       </c>
@@ -61776,7 +61775,7 @@
         <v>787238.2</v>
       </c>
     </row>
-    <row r="221" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A221" s="7" t="s">
         <v>1030</v>
       </c>
@@ -62025,7 +62024,7 @@
         <v>787239.2</v>
       </c>
     </row>
-    <row r="222" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
         <v>1033</v>
       </c>
@@ -62286,7 +62285,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="223" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A223" s="7" t="s">
         <v>1037</v>
       </c>
@@ -62543,7 +62542,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="224" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
         <v>1041</v>
       </c>
@@ -62788,7 +62787,7 @@
         <v>787242.2</v>
       </c>
     </row>
-    <row r="225" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A225" s="7" t="s">
         <v>1046</v>
       </c>
@@ -63049,7 +63048,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="226" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
         <v>1051</v>
       </c>
@@ -63310,7 +63309,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="227" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>1055</v>
       </c>
@@ -63571,7 +63570,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="228" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A228" s="7" t="s">
         <v>1059</v>
       </c>
@@ -63832,7 +63831,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="229" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
         <v>1063</v>
       </c>
@@ -64093,7 +64092,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="230" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A230" s="7" t="s">
         <v>1067</v>
       </c>
@@ -64354,7 +64353,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="231" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
         <v>1072</v>
       </c>
@@ -64613,7 +64612,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="232" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
         <v>1076</v>
       </c>
@@ -64862,7 +64861,7 @@
         <v>787250.2</v>
       </c>
     </row>
-    <row r="233" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A233" s="7" t="s">
         <v>1080</v>
       </c>
@@ -65119,7 +65118,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="234" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
         <v>1087</v>
       </c>
@@ -65380,7 +65379,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="235" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>1091</v>
       </c>
@@ -65629,7 +65628,7 @@
         <v>787253.2</v>
       </c>
     </row>
-    <row r="236" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A236" s="7" t="s">
         <v>1095</v>
       </c>
@@ -65878,7 +65877,7 @@
         <v>787254.2</v>
       </c>
     </row>
-    <row r="237" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>1099</v>
       </c>
@@ -66127,7 +66126,7 @@
         <v>787255.2</v>
       </c>
     </row>
-    <row r="238" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A238" s="7" t="s">
         <v>1103</v>
       </c>
@@ -66376,7 +66375,7 @@
         <v>787256.2</v>
       </c>
     </row>
-    <row r="239" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>1107</v>
       </c>
@@ -66621,7 +66620,7 @@
         <v>787257.2</v>
       </c>
     </row>
-    <row r="240" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A240" s="7" t="s">
         <v>1111</v>
       </c>
@@ -66870,7 +66869,7 @@
         <v>787258.2</v>
       </c>
     </row>
-    <row r="241" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A241" s="7" t="s">
         <v>1116</v>
       </c>
@@ -67115,7 +67114,7 @@
         <v>787259.2</v>
       </c>
     </row>
-    <row r="242" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>1124</v>
       </c>
@@ -67364,7 +67363,7 @@
         <v>787260.2</v>
       </c>
     </row>
-    <row r="243" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A243" s="7" t="s">
         <v>1130</v>
       </c>
@@ -67613,7 +67612,7 @@
         <v>787261.2</v>
       </c>
     </row>
-    <row r="244" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>1134</v>
       </c>
@@ -67860,7 +67859,7 @@
         <v>787262.2</v>
       </c>
     </row>
-    <row r="245" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A245" s="7" t="s">
         <v>1138</v>
       </c>
@@ -68109,7 +68108,7 @@
         <v>787263.2</v>
       </c>
     </row>
-    <row r="246" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>1142</v>
       </c>
@@ -68358,7 +68357,7 @@
         <v>787264.2</v>
       </c>
     </row>
-    <row r="247" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A247" s="7" t="s">
         <v>1147</v>
       </c>
@@ -68852,7 +68851,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="249" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>1156</v>
       </c>
@@ -69113,7 +69112,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="250" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A250" s="2" t="s">
         <v>1160</v>
       </c>
@@ -69362,7 +69361,7 @@
         <v>787268.2</v>
       </c>
     </row>
-    <row r="251" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A251" s="7" t="s">
         <v>1165</v>
       </c>
@@ -69605,7 +69604,7 @@
         <v>787269.2</v>
       </c>
     </row>
-    <row r="252" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>1169</v>
       </c>
@@ -69854,7 +69853,7 @@
         <v>787270.2</v>
       </c>
     </row>
-    <row r="253" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A253" s="7" t="s">
         <v>1173</v>
       </c>
@@ -70103,7 +70102,7 @@
         <v>787271.2</v>
       </c>
     </row>
-    <row r="254" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A254" s="2" t="s">
         <v>1177</v>
       </c>
@@ -70350,7 +70349,7 @@
         <v>787272.2</v>
       </c>
     </row>
-    <row r="255" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A255" s="7" t="s">
         <v>1181</v>
       </c>
@@ -70599,7 +70598,7 @@
         <v>787273.2</v>
       </c>
     </row>
-    <row r="256" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A256" s="2" t="s">
         <v>1185</v>
       </c>
@@ -70848,7 +70847,7 @@
         <v>787274.2</v>
       </c>
     </row>
-    <row r="257" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A257" s="7" t="s">
         <v>1189</v>
       </c>
@@ -71095,7 +71094,7 @@
         <v>787275.2</v>
       </c>
     </row>
-    <row r="258" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>1196</v>
       </c>
@@ -71334,7 +71333,7 @@
         <v>787276.2</v>
       </c>
     </row>
-    <row r="259" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>1201</v>
       </c>
@@ -71583,7 +71582,7 @@
         <v>787277.2</v>
       </c>
     </row>
-    <row r="260" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>1207</v>
       </c>
@@ -71830,7 +71829,7 @@
         <v>787278.2</v>
       </c>
     </row>
-    <row r="261" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A261" s="7" t="s">
         <v>1189</v>
       </c>
@@ -72089,7 +72088,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="262" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A262" s="2" t="s">
         <v>1196</v>
       </c>
@@ -72340,7 +72339,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="263" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>1201</v>
       </c>
@@ -72601,7 +72600,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="264" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>1207</v>
       </c>
@@ -72860,7 +72859,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="265" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A265" s="2" t="s">
         <v>405</v>
       </c>
@@ -73113,7 +73112,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="266" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>405</v>
       </c>
@@ -73366,7 +73365,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="267" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A267" s="2" t="s">
         <v>405</v>
       </c>
@@ -73619,7 +73618,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="268" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A268" s="2" t="s">
         <v>405</v>
       </c>
@@ -73872,7 +73871,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="269" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A269" s="2" t="s">
         <v>405</v>
       </c>
@@ -74125,7 +74124,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="270" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A270" s="2" t="s">
         <v>405</v>
       </c>
@@ -74378,7 +74377,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="271" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A271" s="2" t="s">
         <v>405</v>
       </c>
@@ -74631,7 +74630,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="272" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A272" s="2" t="s">
         <v>405</v>
       </c>
@@ -74884,7 +74883,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="273" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A273" s="2" t="s">
         <v>405</v>
       </c>
@@ -75137,7 +75136,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="274" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A274" s="2" t="s">
         <v>405</v>
       </c>
@@ -75390,7 +75389,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="275" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A275" s="2" t="s">
         <v>405</v>
       </c>
@@ -79420,7 +79419,7 @@
         <v>787266.2</v>
       </c>
     </row>
-    <row r="291" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A291" s="2" t="s">
         <v>405</v>
       </c>
@@ -79673,7 +79672,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="292" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>405</v>
       </c>
@@ -79926,7 +79925,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="293" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>405</v>
       </c>
@@ -80179,7 +80178,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="294" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>405</v>
       </c>
@@ -80432,7 +80431,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="295" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>405</v>
       </c>
@@ -80685,7 +80684,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="296" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>405</v>
       </c>
@@ -80938,7 +80937,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="297" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>405</v>
       </c>
@@ -81191,7 +81190,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="298" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>405</v>
       </c>
@@ -81444,7 +81443,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="299" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>405</v>
       </c>
@@ -81644,7 +81643,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="300" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A300" s="2" t="s">
         <v>405</v>
       </c>
@@ -81844,7 +81843,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="301" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>405</v>
       </c>
@@ -82044,7 +82043,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="302" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>405</v>
       </c>
@@ -82244,7 +82243,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="303" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A303" s="2" t="s">
         <v>405</v>
       </c>
@@ -82444,7 +82443,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="304" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>405</v>
       </c>
@@ -82644,7 +82643,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="305" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
         <v>405</v>
       </c>
@@ -82844,7 +82843,7 @@
         <v>46219</v>
       </c>
     </row>
-    <row r="306" spans="1:89" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:89" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
         <v>405</v>
       </c>
@@ -88183,13 +88182,7 @@
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A258:N258 A262:F262 H262:N262" name="All Access Jorge H_98" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
     <protectedRange algorithmName="SHA-512" hashValue="X6Y1Jx4JNT1HDrvMixQ21UZ7W3nw6S2dYKs7tWghwkPBAMRRX8Zxee4vPMCM9yPAj8Uqi47ZLs4chJ+PaZXoZg==" saltValue="OvWvks2kXCTcZVuV6PedDw==" spinCount="100000" sqref="A259:N259 A263:F263 H263:N263" name="All Access Jorge H_99" securityDescriptor="O:WDG:WDD:(A;;CC;;;S-1-5-21-436374069-1417001333-725345543-136003244)"/>
   </protectedRanges>
-  <autoFilter ref="A1:CK306" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}">
-    <filterColumn colId="6">
-      <filters>
-        <filter val="Cerrado"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:CK326" xr:uid="{5A45D9DC-E8AF-436A-91D0-388125A4A950}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="A1">
     <cfRule type="duplicateValues" dxfId="3" priority="4"/>
